--- a/data/trans_orig/IP1014-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Clase-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92849</t>
+          <t>92798</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197138</t>
+          <t>197111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82731</t>
+          <t>83100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170058</t>
+          <t>170106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197498</t>
+          <t>197515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198543</t>
+          <t>198595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398141</t>
+          <t>397767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123094</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227855</t>
+          <t>227159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,42 +2810,42 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>7765</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7351</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635636</t>
+          <t>635218</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,47 +2918,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>681204</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>676838</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>683261</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>99,5%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>681204</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>677252</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>683284</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1315305</t>
+          <t>1314710</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1322114</t>
+          <t>1322082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86109</t>
+          <t>85479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174989</t>
+          <t>174184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90190</t>
+          <t>90223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186606</t>
+          <t>186135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>220139</t>
+          <t>221095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>226196</t>
+          <t>226246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>426311</t>
+          <t>426512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431819</t>
+          <t>431820</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145514</t>
+          <t>145512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134715</t>
+          <t>134484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282927</t>
+          <t>282978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288347</t>
+          <t>288353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>668688</t>
+          <t>669362</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>704284</t>
+          <t>704551</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711474</t>
+          <t>711605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1376325</t>
+          <t>1376807</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1384765</t>
+          <t>1384680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138544</t>
+          <t>138997</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274865</t>
+          <t>274909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>705330</t>
+          <t>704857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1377346</t>
+          <t>1377331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">

--- a/data/trans_orig/IP1014-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1352</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4747</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4731</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4787</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>96193</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>92821</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>96193</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>92798</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197111</t>
+          <t>197167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2870</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85328</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82711</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85328</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83100</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170106</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3537</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3479</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4165</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5040</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>201374</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>198537</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200091</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>197515</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197505</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201374</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>198595</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>605</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>397767</t>
+          <t>398642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3519</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126584</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>123769</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126584</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123770</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227159</t>
+          <t>227884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,74 +2780,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7885</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3638</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7765</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>681204</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>676718</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>683254</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>952</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>638214</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>635218</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>635630</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,9%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>681204</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>676838</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>683261</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1976</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314710</t>
+          <t>1314880</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1322082</t>
+          <t>1321496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,107 +3357,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>793</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>793</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4284</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3979</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4019</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>88970</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>85798</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>88970</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>85479</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174184</t>
+          <t>174224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,107 +3700,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2506</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2699</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2254</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2705</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3813,74 +3813,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92286</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90223</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>90030</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>273</t>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186135</t>
+          <t>186586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,84 +4386,84 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2557</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5769</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2557</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
           <t>672</t>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>224307</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>221055</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>226236</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>224307</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>221095</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>226246</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>426512</t>
+          <t>426059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3657</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4923</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5350</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4842,74 +4842,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>138493</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>135127</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>148273</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>145512</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>144246</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,4%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>138493</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>134484</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>405</t>
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282978</t>
+          <t>282599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288353</t>
+          <t>288342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9608</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4719</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>8950</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>708810</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>703893</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>711479</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>672742</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>669362</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>669378</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>708810</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>704551</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>711605</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1982</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1376807</t>
+          <t>1376848</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1384680</t>
+          <t>1384744</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7134,47 +7134,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,107 +7364,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4091</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4671</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4373</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>141808</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>138549</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>141808</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>138997</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274909</t>
+          <t>274611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,107 +8050,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4880</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4443</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3908</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>708457</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>705182</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>708457</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>704857</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1377331</t>
+          <t>1376796</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
